--- a/estandar-a/templates/1-4-6-hoja-de-ruta.xlsx
+++ b/estandar-a/templates/1-4-6-hoja-de-ruta.xlsx
@@ -12,7 +12,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tu turno · preguntas guía" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cronograma Gantt · semanas del " sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cronograma Gantt · semanas del '!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -29,17 +34,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <color rgb="004B5563"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,8 +57,13 @@
         <fgColor rgb="0028467E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,16 +71,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3E4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3E4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -445,7 +473,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mi CompañIA</t>
@@ -482,7 +510,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MiPyME</t>
@@ -529,7 +557,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -560,17 +588,17 @@
       <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Operación del proceso CON la solución Por cada solución: descripción de cómo quedará el proceso después de implementada.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -586,17 +614,17 @@
       <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Actividades y responsables por fase Lista granular de actividades. Quién hace qué de tu lado + del lado de la MiPyME.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -612,17 +640,17 @@
       <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Recursos tecnológicos / humanos / financieros Equipo, suscripciones, plataformas, equipo humano, presupuesto desglosado por fase.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -668,7 +696,7 @@
     <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -767,25 +795,25 @@
       <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -809,25 +837,25 @@
       <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -851,25 +879,25 @@
       <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -893,25 +921,25 @@
       <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
